--- a/seo-texts/guest-posts/DONORS-FOR-PICK.xlsx
+++ b/seo-texts/guest-posts/DONORS-FOR-PICK.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -658,8 +658,6 @@
           <t>размещений в выборке нет — просить пример; конвейер</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -893,8 +891,6 @@
           <t>ссылки не проверены — просить пример размещения</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -940,8 +936,6 @@
           <t>в своих статьях nofollow (14%) — требовать гарантию</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -987,8 +981,6 @@
           <t>размещений в выборке нет — просить пример</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1081,8 +1073,6 @@
           <t>в своих статьях nofollow (0%) — требовать гарантию</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1128,8 +1118,6 @@
           <t>ссылки открыты</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1175,8 +1163,6 @@
           <t>ссылки не проверены — просить пример размещения</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1222,8 +1208,6 @@
           <t>размещений в выборке нет — просить пример; конвейер</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1234,7 +1218,6 @@
           <t>gorod24.online</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>феодосия, симферополь, симферополь новости, новости крыма, севастополь сейчас</t>
@@ -1265,8 +1248,6 @@
           <t>ссылки не проверены — просить пример размещения; конвейер</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1312,8 +1293,6 @@
           <t>в своих статьях nofollow (0%) — требовать гарантию</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1359,8 +1338,6 @@
           <t>ссылки открыты; конвейер</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1406,8 +1383,6 @@
           <t>размещений в выборке нет — просить пример; конвейер</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1418,7 +1393,6 @@
           <t>get-color.ru</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>#ff0000, #c0c0c0, розовый цвет, цвет, цвета</t>
@@ -1449,73 +1423,69 @@
           <t>ссылки не проверены — просить пример размещения</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>4x4.media</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Журнал Клуб 4х4 - всё о внедорожниках</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>нива, ineos grenadier, самые уродливые машины, land cruiser, jetour t1</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>смежная</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>1700</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>5200</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>размещений в выборке нет — просить пример</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="A22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>nashaplaneta.net</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Наша &amp;#127757; Планета | путеводитель для самостоятельных путешествий</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>экзотические фрукты, экзотические фрукты, село молочное, фукуок, туапсе на карте</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>мимо</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>40</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9717</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1087</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3590</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>в своих статьях nofollow (0%) — требовать гарантию; конвейер</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nashaplaneta.net</t>
+          <t>nanya.ru</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Наша &amp;#127757; Планета | путеводитель для самостоятельных путешествий</t>
+          <t>Портал няня.ру - свежие статьи и советы для профессиональных нянь и ро</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>экзотические фрукты, экзотические фрукты, село молочное, фукуок, туапсе на карте</t>
+          <t>няня, кормить ребенка грудью во сне, 3 сумки в роддом что куда класть, резюме няня, пол ребенка калькулятор</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1524,45 +1494,43 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>9717</v>
+        <v>2200</v>
       </c>
       <c r="H23" t="n">
-        <v>1087</v>
+        <v>1387</v>
       </c>
       <c r="I23" t="n">
-        <v>3590</v>
+        <v>2700</v>
       </c>
       <c r="J23" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (0%) — требовать гарантию; конвейер</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+          <t>ссылки открыты; конвейер</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nanya.ru</t>
+          <t>twizz.ru</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Портал няня.ру - свежие статьи и советы для профессиональных нянь и ро</t>
+          <t>Twizz &amp;#8212; новости, истории, тренды интернета</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>няня, кормить ребенка грудью во сне, 3 сумки в роддом что куда класть, резюме няня, пол ребенка калькулятор</t>
+          <t>мемные коты, ugly hot, фотки, возраст кошки по человеческим меркам, моника беллуччи в молодости</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1571,45 +1539,43 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G24" t="n">
-        <v>2200</v>
+        <v>9283</v>
       </c>
       <c r="H24" t="n">
-        <v>1387</v>
+        <v>77</v>
       </c>
       <c r="I24" t="n">
-        <v>2700</v>
+        <v>4000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ссылки открыты; конвейер</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+          <t>ссылки открыты</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>twizz.ru</t>
+          <t>kikonline.ru</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Twizz &amp;#8212; новости, истории, тренды интернета</t>
+          <t>Новости Кургана и Курганской области | Газета Курган и курганцы</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>мемные коты, ugly hot, фотки, возраст кошки по человеческим меркам, моника беллуччи в молодости</t>
+          <t>новости кургана, курганская область, новости курган, курган новости, новости кургана сегодня</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1618,45 +1584,43 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G25" t="n">
-        <v>9283</v>
+        <v>2498</v>
       </c>
       <c r="H25" t="n">
-        <v>77</v>
+        <v>2667</v>
       </c>
       <c r="I25" t="n">
-        <v>4000</v>
+        <v>3100</v>
       </c>
       <c r="J25" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ссылки открыты</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+          <t>ссылки открыты; конвейер</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kikonline.ru</t>
+          <t>mirnov.ru</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Новости Кургана и Курганской области | Газета Курган и курганцы</t>
+          <t>Издательство «Мир новостей» — Главные новости в России и мире</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>новости кургана, курганская область, новости курган, курган новости, новости кургана сегодня</t>
+          <t>новости шоу бизнеса, гороскоп, светские новости, новости шоу-бизнеса скандалы светская хроника, новости шоу бизнеса</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1665,16 +1629,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G26" t="n">
-        <v>2498</v>
+        <v>5963</v>
       </c>
       <c r="H26" t="n">
-        <v>2667</v>
+        <v>1673</v>
       </c>
       <c r="I26" t="n">
-        <v>3100</v>
+        <v>3604</v>
       </c>
       <c r="J26" t="n">
         <v>1.46</v>
@@ -1684,26 +1648,24 @@
           <t>ссылки открыты; конвейер</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mirnov.ru</t>
+          <t>rewizor.ru</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Издательство «Мир новостей» — Главные новости в России и мире</t>
+          <t>РЕВИЗОР.РУ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>новости шоу бизнеса, гороскоп, светские новости, новости шоу-бизнеса скандалы светская хроника, новости шоу бизнеса</t>
+          <t>якубович, уитни хьюстон, леонид якубович, гомер, анатолий прохоров</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1712,45 +1674,43 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
-        <v>5963</v>
+        <v>4754</v>
       </c>
       <c r="H27" t="n">
-        <v>1673</v>
+        <v>421</v>
       </c>
       <c r="I27" t="n">
-        <v>3604</v>
+        <v>4400</v>
       </c>
       <c r="J27" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ссылки открыты; конвейер</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rewizor.ru</t>
+          <t>berkat.ru</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>РЕВИЗОР.РУ</t>
+          <t>Объявления, реклама Ингушетии. Недвижимость, работа, авто, вакансии Be</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>якубович, уитни хьюстон, леонид якубович, гомер, анатолий прохоров</t>
+          <t>беркат, беркат ру, беркат работа, беркат вакансии, работа в ингушетии</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1759,135 +1719,128 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G28" t="n">
-        <v>4754</v>
+        <v>8265</v>
       </c>
       <c r="H28" t="n">
-        <v>421</v>
+        <v>273</v>
       </c>
       <c r="I28" t="n">
-        <v>4400</v>
+        <v>4004</v>
       </c>
       <c r="J28" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+          <t>ссылки открыты</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>berkat.ru</t>
+          <t>арктик-тв.рф</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Объявления, реклама Ингушетии. Недвижимость, работа, авто, вакансии Be</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>беркат, беркат ру, беркат работа, беркат вакансии, работа в ингушетии</t>
+          <t>Арктик-ТВ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>мимо</t>
+          <t>?</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>8265</v>
+        <v>3538</v>
       </c>
       <c r="H29" t="n">
-        <v>273</v>
+        <v>74</v>
       </c>
       <c r="I29" t="n">
-        <v>4004</v>
+        <v>4000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>ссылки открыты</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>арктик-тв.рф</t>
+          <t>omskgazzeta.ru</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Арктик-ТВ</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Главная - Вечерний Омск</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>новости сво, чп омск, берег драверта, матчи кхл, обрушение казармы в омске</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>мимо</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G30" t="n">
-        <v>3538</v>
+        <v>19143</v>
       </c>
       <c r="H30" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I30" t="n">
-        <v>4000</v>
+        <v>5400</v>
       </c>
       <c r="J30" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ссылки открыты</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>omskgazzeta.ru</t>
+          <t>sochistream.ru</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Главная - Вечерний Омск</t>
+          <t>СочиСтрим.ру - Все новости Сочи и Краснодарского края</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>новости сво, чп омск, берег драверта, матчи кхл, обрушение казармы в омске</t>
+          <t>беспилотный летательный аппарат, крымский мост, геленджик, новости сочи, сочи</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1896,45 +1849,43 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>19143</v>
+        <v>30708</v>
       </c>
       <c r="H31" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="I31" t="n">
-        <v>5400</v>
+        <v>7000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+          <t>размещений в выборке нет — просить пример</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sochistream.ru</t>
+          <t>anaparegion.ru</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>СочиСтрим.ру - Все новости Сочи и Краснодарского края</t>
+          <t>Актуальные новости Анапы и Анапского района</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>беспилотный летательный аппарат, крымский мост, геленджик, новости сочи, сочи</t>
+          <t>анапа, новости анапа, новости анапы, анапа новости, анапа</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1943,45 +1894,38 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G32" t="n">
-        <v>30708</v>
+        <v>3586</v>
       </c>
       <c r="H32" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="I32" t="n">
-        <v>7000</v>
+        <v>5200</v>
       </c>
       <c r="J32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>размещений в выборке нет — просить пример</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>anaparegion.ru</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Актуальные новости Анапы и Анапского района</t>
+          <t>rk.karelia.ru</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>анапа, новости анапа, новости анапы, анапа новости, анапа</t>
+          <t>карелия, заморозки, путин, петрозаводск, финно</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1990,41 +1934,43 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="G33" t="n">
-        <v>3586</v>
+        <v>3537</v>
       </c>
       <c r="H33" t="n">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="I33" t="n">
-        <v>5200</v>
+        <v>6500</v>
       </c>
       <c r="J33" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>размещений в выборке нет — просить пример</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+          <t>ссылки не проверены — просить пример размещения</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>rk.karelia.ru</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>bookmix.ru</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Книги - рецензии, обзоры, отзывы, книжные рейтинги и рекомендации</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>карелия, заморозки, путин, петрозаводск, финно</t>
+          <t>консуэло сегура, эркюль пуаро, смешные слова, короткие рассказы со смыслом, манга</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2033,45 +1979,43 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G34" t="n">
-        <v>3537</v>
+        <v>8308</v>
       </c>
       <c r="H34" t="n">
-        <v>165</v>
+        <v>301</v>
       </c>
       <c r="I34" t="n">
         <v>6500</v>
       </c>
       <c r="J34" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>ссылки не проверены — просить пример размещения</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+          <t>размещений в выборке нет — просить пример</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bookmix.ru</t>
+          <t>kvartblog.ru</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Книги - рецензии, обзоры, отзывы, книжные рейтинги и рекомендации</t>
+          <t>Квартблог – интернет-журнал об обустройстве дома, интерьерах и декоре</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>консуэло сегура, эркюль пуаро, смешные слова, короткие рассказы со смыслом, манга</t>
+          <t>гардина, зеленый цвет, оттенки зеленого, детская комната для мальчика, молдинги на стену</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2080,45 +2024,43 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G35" t="n">
-        <v>8308</v>
+        <v>2887</v>
       </c>
       <c r="H35" t="n">
-        <v>301</v>
+        <v>375</v>
       </c>
       <c r="I35" t="n">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="J35" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>размещений в выборке нет — просить пример</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+          <t>в своих статьях nofollow (18%) — требовать гарантию</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kvartblog.ru</t>
+          <t>bv02.info</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Квартблог – интернет-журнал об обустройстве дома, интерьерах и декоре</t>
+          <t>Баймакский вестник - новости Баймакского района Республики Башкортоста</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>гардина, зеленый цвет, оттенки зеленого, детская комната для мальчика, молдинги на стену</t>
+          <t>новости башкирии, командование, новости башкирии, стерлитамак новости, гладков белгород</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2127,63 +2069,61 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G36" t="n">
-        <v>2887</v>
+        <v>2721</v>
       </c>
       <c r="H36" t="n">
-        <v>375</v>
+        <v>8</v>
       </c>
       <c r="I36" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (18%) — требовать гарантию</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+          <t>ссылки открыты</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>37</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>bm24.ru</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>рождество николая чудотворца, иоанн шанхайский, нечаянная радость икона, зерновой элеватор, день владимирской иконы</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>мимо</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>bv02.info</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Баймакский вестник - новости Баймакского района Республики Башкортоста</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>новости башкирии, командование, новости башкирии, стерлитамак новости, гладков белгород</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>мимо</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
+        <v>2115</v>
+      </c>
+      <c r="H37" t="n">
         <v>25</v>
       </c>
-      <c r="G37" t="n">
-        <v>2721</v>
-      </c>
-      <c r="H37" t="n">
-        <v>8</v>
-      </c>
       <c r="I37" t="n">
-        <v>5500</v>
+        <v>5900</v>
       </c>
       <c r="J37" t="n">
         <v>0.88</v>
@@ -2193,26 +2133,24 @@
           <t>ссылки открыты</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bm24.ru</t>
+          <t>ecoportal.info</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Главная</t>
+          <t>Экологический портал - ECOportal.info | Сайт об экологии, растительном</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>рождество николая чудотворца, иоанн шанхайский, нечаянная радость икона, зерновой элеватор, день владимирской иконы</t>
+          <t>хищные птицы беларуси, гиена, амазонка животные, травоядные животные, птицы подмосковья</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2221,45 +2159,43 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G38" t="n">
-        <v>2115</v>
+        <v>10330</v>
       </c>
       <c r="H38" t="n">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="I38" t="n">
-        <v>5900</v>
+        <v>6700</v>
       </c>
       <c r="J38" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ссылки открыты</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+          <t>размещений в выборке нет — просить пример</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ecoportal.info</t>
+          <t>globalkras.ru</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Экологический портал - ECOportal.info | Сайт об экологии, растительном</t>
+          <t>ГлобалКРАС.ру: Можно ли заработать на монетах из драгметаллов - Красно</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>хищные птицы беларуси, гиена, амазонка животные, травоядные животные, птицы подмосковья</t>
+          <t>гороскоп близнецы, гороскоп весы, гороскоп рак, гороскоп близнецы на сегодня, гороскоп лев</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2268,45 +2204,43 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G39" t="n">
-        <v>10330</v>
+        <v>2466</v>
       </c>
       <c r="H39" t="n">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="I39" t="n">
-        <v>6700</v>
+        <v>7000</v>
       </c>
       <c r="J39" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>размещений в выборке нет — просить пример</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+          <t>ссылки открыты</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>globalkras.ru</t>
+          <t>vremya.press</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ГлобалКРАС.ру: Можно ли заработать на монетах из драгметаллов - Красно</t>
+          <t>Главные новости Урфо, России и мира сегодня - Время PRESS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>гороскоп близнецы, гороскоп весы, гороскоп рак, гороскоп близнецы на сегодня, гороскоп лев</t>
+          <t>удар возмездия по украине, новости дня сегодня, в крыму ужасная трагедия сегодня, прописка, с 1 июля</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2315,13 +2249,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G40" t="n">
-        <v>2466</v>
+        <v>2548</v>
       </c>
       <c r="H40" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="I40" t="n">
         <v>7000</v>
@@ -2334,26 +2268,24 @@
           <t>ссылки открыты</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>vremya.press</t>
+          <t>prostudio.ru</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Главные новости Урфо, России и мира сегодня - Время PRESS</t>
+          <t>Digital-агентство Prostudio — Ваш проводник в диджитал</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>удар возмездия по украине, новости дня сегодня, в крыму ужасная трагедия сегодня, прописка, с 1 июля</t>
+          <t>краш это, поколения по годам, сравнение текстов, краш, сравнение текстов онлайн</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2362,121 +2294,72 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G41" t="n">
-        <v>2548</v>
+        <v>7194</v>
       </c>
       <c r="H41" t="n">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="I41" t="n">
-        <v>7000</v>
+        <v>5990</v>
       </c>
       <c r="J41" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>ссылки открыты</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prostudio.ru</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Digital-агентство Prostudio — Ваш проводник в диджитал</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>краш это, поколения по годам, сравнение текстов, краш, сравнение текстов онлайн</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>мимо</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>39</v>
-      </c>
-      <c r="G42" t="n">
-        <v>7194</v>
-      </c>
-      <c r="H42" t="n">
-        <v>177</v>
-      </c>
-      <c r="I42" t="n">
-        <v>5990</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>ссылки открыты</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A42" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>fgisrf.ru</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Справочник расценок #1</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>ферм, установка окон пвх расценка в смете, демонтаж плинтуса расценка в смете, демонтаж кирпичной кладки смета, рас</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>смежная</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F42" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>2059</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I42" s="2" t="n">
         <v>2600</v>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="J42" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>размещений в выборке нет — просить пример</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5680,7 +5563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5977,6 +5860,23 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4x4.media</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>решение владельца</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5200 ₽ при 5-8% нашей аудитории — дорого для слабой связи</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seo-texts/guest-posts/DONORS-FOR-PICK.xlsx
+++ b/seo-texts/guest-posts/DONORS-FOR-PICK.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -801,69 +801,67 @@
       <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>miniteh.com</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Browser verification</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>военный камаз, купить урал с военного хранения, купить военную технику, урал с хранения, купить военный камаз</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>смежная</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>589</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>kakoj-segodnja-prazdnik.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Just a moment...</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>какой сегодня праздник, праздник сегодня, какой сегодня праздник, праздники сегодня, какой сегодня праздник</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>мимо</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>37</v>
+      </c>
+      <c r="G8" t="n">
+        <v>125496</v>
+      </c>
+      <c r="H8" t="n">
+        <v>37</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>ссылки не проверены — просить пример размещения</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kakoj-segodnja-prazdnik.com</t>
+          <t>gamebox.biz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Just a moment...</t>
+          <t>Обзоры, анонсы и новости мобильных игр на Gamebox.biz</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>какой сегодня праздник, праздник сегодня, какой сегодня праздник, праздники сегодня, какой сегодня праздник</t>
+          <t>слово из 5 букв тинькофф сегодня, 5 букв тинькофф сегодня, слово из 5 букв тинькофф, 5 букв тинькофф, пять букв тин</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -872,43 +870,43 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>125496</v>
+        <v>3948</v>
       </c>
       <c r="H9" t="n">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="I9" t="n">
-        <v>2900</v>
+        <v>2200</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ссылки не проверены — просить пример размещения</t>
+          <t>в своих статьях nofollow (14%) — требовать гарантию</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gamebox.biz</t>
+          <t>citaty.info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Обзоры, анонсы и новости мобильных игр на Gamebox.biz</t>
+          <t>Цитаты.инфо — дом цитат</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>слово из 5 букв тинькофф сегодня, 5 букв тинькофф сегодня, слово из 5 букв тинькофф, 5 букв тинькофф, пять букв тин</t>
+          <t>цитаты стетхема, мактрахер, джейсон стетхем цитаты, цитаты, дюдюка</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -917,135 +915,135 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>3948</v>
+        <v>141185</v>
       </c>
       <c r="H10" t="n">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="I10" t="n">
-        <v>2200</v>
+        <v>4000</v>
       </c>
       <c r="J10" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (14%) — требовать гарантию</t>
+          <t>размещений в выборке нет — просить пример</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>citaty.info</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Цитаты.инфо — дом цитат</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>цитаты стетхема, мактрахер, джейсон стетхем цитаты, цитаты, дюдюка</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="A11" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>galan.ru</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Галан - электрические отопительные котлы</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>фановая труба, галан, ремонт производственных зданий и помещений, электродный котел, фановая труба в частном доме</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>смежная</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>584</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>размещений в выборке нет — просить пример</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>guidesgame.ru</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GuidesGame — коды подарков и бонусов для игр</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>коды шиндо лайф, шиндо лайф коды, коды юба, коды блю лок ривалс, шиндо лайф коды</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>мимо</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>71</v>
-      </c>
-      <c r="G11" t="n">
-        <v>141185</v>
-      </c>
-      <c r="H11" t="n">
-        <v>41</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>размещений в выборке нет — просить пример</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>galan.ru</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Галан - электрические отопительные котлы</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>фановая труба, галан, ремонт производственных зданий и помещений, электродный котел, фановая труба в частном доме</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>смежная</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>584</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>264</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>980</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>размещений в выборке нет — просить пример</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4485</v>
+      </c>
+      <c r="H12" t="n">
+        <v>123</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2162</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>guidesgame.ru</t>
+          <t>mir76.ru</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GuidesGame — коды подарков и бонусов для игр</t>
+          <t>Сайт Ярославля: город онлайн | Ярославль онлайн mir76.ru</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>коды шиндо лайф, шиндо лайф коды, коды юба, коды блю лок ривалс, шиндо лайф коды</t>
+          <t>аптечная справка ярославль, ярославль, циан ярославль, карта ярославля, аптечная справка рыбинск</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1054,43 +1052,43 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>4485</v>
+        <v>2970</v>
       </c>
       <c r="H13" t="n">
-        <v>123</v>
+        <v>401</v>
       </c>
       <c r="I13" t="n">
-        <v>2162</v>
+        <v>2490</v>
       </c>
       <c r="J13" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
+          <t>ссылки открыты</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mir76.ru</t>
+          <t>satom.ru</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Сайт Ярославля: город онлайн | Ярославль онлайн mir76.ru</t>
+          <t>Проверка безопасности</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>аптечная справка ярославль, ярославль, циан ярославль, карта ярославля, аптечная справка рыбинск</t>
+          <t>лучшие презервативы, крыльцо к дому, как клеить обои, пульверизатор, беседка из металла</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1099,43 +1097,43 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>2970</v>
+        <v>6291</v>
       </c>
       <c r="H14" t="n">
-        <v>401</v>
+        <v>244</v>
       </c>
       <c r="I14" t="n">
-        <v>2490</v>
+        <v>3500</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ссылки открыты</t>
+          <t>ссылки не проверены — просить пример размещения</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>satom.ru</t>
+          <t>moluch.ru</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Проверка безопасности</t>
+          <t>Публикация научных статей — Молодой ученый</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>лучшие презервативы, крыльцо к дому, как клеить обои, пульверизатор, беседка из металла</t>
+          <t>инстаграм анонимно, истории инстаграм анонимно, смотреть инстаграм анонимно, анонимно сторис, анонимный просмотр ст</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1144,43 +1142,38 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>6291</v>
+        <v>18636</v>
       </c>
       <c r="H15" t="n">
-        <v>244</v>
+        <v>1792</v>
       </c>
       <c r="I15" t="n">
         <v>3500</v>
       </c>
       <c r="J15" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>ссылки не проверены — просить пример размещения</t>
+          <t>размещений в выборке нет — просить пример; конвейер</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>moluch.ru</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Публикация научных статей — Молодой ученый</t>
+          <t>gorod24.online</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>инстаграм анонимно, истории инстаграм анонимно, смотреть инстаграм анонимно, анонимно сторис, анонимный просмотр ст</t>
+          <t>феодосия, симферополь, симферополь новости, новости крыма, севастополь сейчас</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1189,38 +1182,43 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>18636</v>
+        <v>5362</v>
       </c>
       <c r="H16" t="n">
-        <v>1792</v>
+        <v>886</v>
       </c>
       <c r="I16" t="n">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="J16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>размещений в выборке нет — просить пример; конвейер</t>
+          <t>ссылки не проверены — просить пример размещения; конвейер</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gorod24.online</t>
+          <t>spark.ru</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SPARK — платформа для общения бизнеса с бизнесом</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>феодосия, симферополь, симферополь новости, новости крыма, севастополь сейчас</t>
+          <t>виртуальный номер, купить виртуальный номер, fansly, глаз бога телеграм, глаз бога бот</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1229,43 +1227,43 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>5362</v>
+        <v>28483</v>
       </c>
       <c r="H17" t="n">
-        <v>886</v>
+        <v>800</v>
       </c>
       <c r="I17" t="n">
-        <v>3300</v>
+        <v>4805</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>ссылки не проверены — просить пример размещения; конвейер</t>
+          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>spark.ru</t>
+          <t>tvcenter.ru</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SPARK — платформа для общения бизнеса с бизнесом</t>
+          <t>TVCenter.ru - Про звёзд, шоубизнес, про знаменитостей и кино, программ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>виртуальный номер, купить виртуальный номер, fansly, глаз бога телеграм, глаз бога бот</t>
+          <t>оксана самойлова, николай лукашенко, анна семенович, ольга бузова, ирина шейк</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1274,43 +1272,43 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>28483</v>
+        <v>13571</v>
       </c>
       <c r="H18" t="n">
-        <v>800</v>
+        <v>1240</v>
       </c>
       <c r="I18" t="n">
-        <v>4805</v>
+        <v>2300</v>
       </c>
       <c r="J18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
+          <t>ссылки открыты; конвейер</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>tvcenter.ru</t>
+          <t>kostroma.today</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TVCenter.ru - Про звёзд, шоубизнес, про знаменитостей и кино, программ</t>
+          <t>KOSTROMA.TODAY — Главные события и новости Костромы</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>оксана самойлова, николай лукашенко, анна семенович, ольга бузова, ирина шейк</t>
+          <t>новости кострома, чп кострома, артем маслов, новости костромы, кострома новости</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1319,43 +1317,38 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>13571</v>
+        <v>5491</v>
       </c>
       <c r="H19" t="n">
-        <v>1240</v>
+        <v>892</v>
       </c>
       <c r="I19" t="n">
-        <v>2300</v>
+        <v>3250</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ссылки открыты; конвейер</t>
+          <t>размещений в выборке нет — просить пример; конвейер</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>kostroma.today</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>KOSTROMA.TODAY — Главные события и новости Костромы</t>
+          <t>get-color.ru</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>новости кострома, чп кострома, артем маслов, новости костромы, кострома новости</t>
+          <t>#ff0000, #c0c0c0, розовый цвет, цвет, цвета</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1367,35 +1360,40 @@
         <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>5491</v>
+        <v>68095</v>
       </c>
       <c r="H20" t="n">
-        <v>892</v>
+        <v>98</v>
       </c>
       <c r="I20" t="n">
-        <v>3250</v>
+        <v>4750</v>
       </c>
       <c r="J20" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>размещений в выборке нет — просить пример; конвейер</t>
+          <t>ссылки не проверены — просить пример размещения</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>get-color.ru</t>
+          <t>nashaplaneta.net</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Наша &amp;#127757; Планета | путеводитель для самостоятельных путешествий</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>#ff0000, #c0c0c0, розовый цвет, цвет, цвета</t>
+          <t>экзотические фрукты, экзотические фрукты, село молочное, фукуок, туапсе на карте</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1404,43 +1402,43 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>68095</v>
+        <v>9717</v>
       </c>
       <c r="H21" t="n">
-        <v>98</v>
+        <v>1087</v>
       </c>
       <c r="I21" t="n">
-        <v>4750</v>
+        <v>3590</v>
       </c>
       <c r="J21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>ссылки не проверены — просить пример размещения</t>
+          <t>в своих статьях nofollow (0%) — требовать гарантию; конвейер</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nashaplaneta.net</t>
+          <t>nanya.ru</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Наша &amp;#127757; Планета | путеводитель для самостоятельных путешествий</t>
+          <t>Портал няня.ру - свежие статьи и советы для профессиональных нянь и ро</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>экзотические фрукты, экзотические фрукты, село молочное, фукуок, туапсе на карте</t>
+          <t>няня, кормить ребенка грудью во сне, 3 сумки в роддом что куда класть, резюме няня, пол ребенка калькулятор</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1449,43 +1447,43 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>9717</v>
+        <v>2200</v>
       </c>
       <c r="H22" t="n">
-        <v>1087</v>
+        <v>1387</v>
       </c>
       <c r="I22" t="n">
-        <v>3590</v>
+        <v>2700</v>
       </c>
       <c r="J22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (0%) — требовать гарантию; конвейер</t>
+          <t>ссылки открыты; конвейер</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nanya.ru</t>
+          <t>twizz.ru</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Портал няня.ру - свежие статьи и советы для профессиональных нянь и ро</t>
+          <t>Twizz &amp;#8212; новости, истории, тренды интернета</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>няня, кормить ребенка грудью во сне, 3 сумки в роддом что куда класть, резюме няня, пол ребенка калькулятор</t>
+          <t>мемные коты, ugly hot, фотки, возраст кошки по человеческим меркам, моника беллуччи в молодости</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1494,43 +1492,43 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G23" t="n">
-        <v>2200</v>
+        <v>9283</v>
       </c>
       <c r="H23" t="n">
-        <v>1387</v>
+        <v>77</v>
       </c>
       <c r="I23" t="n">
-        <v>2700</v>
+        <v>4000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ссылки открыты; конвейер</t>
+          <t>ссылки открыты</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>twizz.ru</t>
+          <t>kikonline.ru</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Twizz &amp;#8212; новости, истории, тренды интернета</t>
+          <t>Новости Кургана и Курганской области | Газета Курган и курганцы</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>мемные коты, ugly hot, фотки, возраст кошки по человеческим меркам, моника беллуччи в молодости</t>
+          <t>новости кургана, курганская область, новости курган, курган новости, новости кургана сегодня</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1539,43 +1537,43 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G24" t="n">
-        <v>9283</v>
+        <v>2498</v>
       </c>
       <c r="H24" t="n">
-        <v>77</v>
+        <v>2667</v>
       </c>
       <c r="I24" t="n">
-        <v>4000</v>
+        <v>3100</v>
       </c>
       <c r="J24" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ссылки открыты</t>
+          <t>ссылки открыты; конвейер</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>kikonline.ru</t>
+          <t>mirnov.ru</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Новости Кургана и Курганской области | Газета Курган и курганцы</t>
+          <t>Издательство «Мир новостей» — Главные новости в России и мире</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>новости кургана, курганская область, новости курган, курган новости, новости кургана сегодня</t>
+          <t>новости шоу бизнеса, гороскоп, светские новости, новости шоу-бизнеса скандалы светская хроника, новости шоу бизнеса</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1584,16 +1582,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G25" t="n">
-        <v>2498</v>
+        <v>5963</v>
       </c>
       <c r="H25" t="n">
-        <v>2667</v>
+        <v>1673</v>
       </c>
       <c r="I25" t="n">
-        <v>3100</v>
+        <v>3604</v>
       </c>
       <c r="J25" t="n">
         <v>1.46</v>
@@ -1606,21 +1604,21 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mirnov.ru</t>
+          <t>rewizor.ru</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Издательство «Мир новостей» — Главные новости в России и мире</t>
+          <t>РЕВИЗОР.РУ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>новости шоу бизнеса, гороскоп, светские новости, новости шоу-бизнеса скандалы светская хроника, новости шоу бизнеса</t>
+          <t>якубович, уитни хьюстон, леонид якубович, гомер, анатолий прохоров</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1629,43 +1627,43 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
-        <v>5963</v>
+        <v>4754</v>
       </c>
       <c r="H26" t="n">
-        <v>1673</v>
+        <v>421</v>
       </c>
       <c r="I26" t="n">
-        <v>3604</v>
+        <v>4400</v>
       </c>
       <c r="J26" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ссылки открыты; конвейер</t>
+          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rewizor.ru</t>
+          <t>berkat.ru</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>РЕВИЗОР.РУ</t>
+          <t>Объявления, реклама Ингушетии. Недвижимость, работа, авто, вакансии Be</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>якубович, уитни хьюстон, леонид якубович, гомер, анатолий прохоров</t>
+          <t>беркат, беркат ру, беркат работа, беркат вакансии, работа в ингушетии</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1674,64 +1672,59 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>4754</v>
+        <v>8265</v>
       </c>
       <c r="H27" t="n">
-        <v>421</v>
+        <v>273</v>
       </c>
       <c r="I27" t="n">
-        <v>4400</v>
+        <v>4004</v>
       </c>
       <c r="J27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
+          <t>ссылки открыты</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>berkat.ru</t>
+          <t>арктик-тв.рф</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Объявления, реклама Ингушетии. Недвижимость, работа, авто, вакансии Be</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>беркат, беркат ру, беркат работа, беркат вакансии, работа в ингушетии</t>
+          <t>Арктик-ТВ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>мимо</t>
+          <t>?</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G28" t="n">
-        <v>8265</v>
+        <v>3538</v>
       </c>
       <c r="H28" t="n">
-        <v>273</v>
+        <v>74</v>
       </c>
       <c r="I28" t="n">
-        <v>4004</v>
+        <v>4000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1741,61 +1734,66 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>арктик-тв.рф</t>
+          <t>omskgazzeta.ru</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Арктик-ТВ</t>
+          <t>Главная - Вечерний Омск</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>новости сво, чп омск, берег драверта, матчи кхл, обрушение казармы в омске</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>мимо</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G29" t="n">
-        <v>3538</v>
+        <v>19143</v>
       </c>
       <c r="H29" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I29" t="n">
-        <v>4000</v>
+        <v>5400</v>
       </c>
       <c r="J29" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>ссылки открыты</t>
+          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>omskgazzeta.ru</t>
+          <t>sochistream.ru</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Главная - Вечерний Омск</t>
+          <t>СочиСтрим.ру - Все новости Сочи и Краснодарского края</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>новости сво, чп омск, берег драверта, матчи кхл, обрушение казармы в омске</t>
+          <t>беспилотный летательный аппарат, крымский мост, геленджик, новости сочи, сочи</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1804,43 +1802,43 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G30" t="n">
-        <v>19143</v>
+        <v>30708</v>
       </c>
       <c r="H30" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="I30" t="n">
-        <v>5400</v>
+        <v>7000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (0%) — требовать гарантию</t>
+          <t>размещений в выборке нет — просить пример</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sochistream.ru</t>
+          <t>anaparegion.ru</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>СочиСтрим.ру - Все новости Сочи и Краснодарского края</t>
+          <t>Актуальные новости Анапы и Анапского района</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>беспилотный летательный аппарат, крымский мост, геленджик, новости сочи, сочи</t>
+          <t>анапа, новости анапа, новости анапы, анапа новости, анапа</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1849,19 +1847,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>30708</v>
+        <v>3586</v>
       </c>
       <c r="H31" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>7000</v>
+        <v>5200</v>
       </c>
       <c r="J31" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1871,21 +1869,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>anaparegion.ru</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Актуальные новости Анапы и Анапского района</t>
+          <t>rk.karelia.ru</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>анапа, новости анапа, новости анапы, анапа новости, анапа</t>
+          <t>карелия, заморозки, путин, петрозаводск, финно</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1894,38 +1887,43 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="G32" t="n">
-        <v>3586</v>
+        <v>3537</v>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="I32" t="n">
-        <v>5200</v>
+        <v>6500</v>
       </c>
       <c r="J32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>размещений в выборке нет — просить пример</t>
+          <t>ссылки не проверены — просить пример размещения</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>rk.karelia.ru</t>
+          <t>bookmix.ru</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Книги - рецензии, обзоры, отзывы, книжные рейтинги и рекомендации</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>карелия, заморозки, путин, петрозаводск, финно</t>
+          <t>консуэло сегура, эркюль пуаро, смешные слова, короткие рассказы со смыслом, манга</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1934,43 +1932,43 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G33" t="n">
-        <v>3537</v>
+        <v>8308</v>
       </c>
       <c r="H33" t="n">
-        <v>165</v>
+        <v>301</v>
       </c>
       <c r="I33" t="n">
         <v>6500</v>
       </c>
       <c r="J33" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>ссылки не проверены — просить пример размещения</t>
+          <t>размещений в выборке нет — просить пример</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bookmix.ru</t>
+          <t>kvartblog.ru</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Книги - рецензии, обзоры, отзывы, книжные рейтинги и рекомендации</t>
+          <t>Квартблог – интернет-журнал об обустройстве дома, интерьерах и декоре</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>консуэло сегура, эркюль пуаро, смешные слова, короткие рассказы со смыслом, манга</t>
+          <t>гардина, зеленый цвет, оттенки зеленого, детская комната для мальчика, молдинги на стену</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1979,43 +1977,43 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G34" t="n">
-        <v>8308</v>
+        <v>2887</v>
       </c>
       <c r="H34" t="n">
-        <v>301</v>
+        <v>375</v>
       </c>
       <c r="I34" t="n">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="J34" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>размещений в выборке нет — просить пример</t>
+          <t>в своих статьях nofollow (18%) — требовать гарантию</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kvartblog.ru</t>
+          <t>bv02.info</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Квартблог – интернет-журнал об обустройстве дома, интерьерах и декоре</t>
+          <t>Баймакский вестник - новости Баймакского района Республики Башкортоста</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>гардина, зеленый цвет, оттенки зеленого, детская комната для мальчика, молдинги на стену</t>
+          <t>новости башкирии, командование, новости башкирии, стерлитамак новости, гладков белгород</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2024,61 +2022,61 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>2887</v>
+        <v>2721</v>
       </c>
       <c r="H35" t="n">
-        <v>375</v>
+        <v>8</v>
       </c>
       <c r="I35" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>в своих статьях nofollow (18%) — требовать гарантию</t>
+          <t>ссылки открыты</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>37</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>bm24.ru</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>рождество николая чудотворца, иоанн шанхайский, нечаянная радость икона, зерновой элеватор, день владимирской иконы</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>мимо</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>36</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>bv02.info</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Баймакский вестник - новости Баймакского района Республики Башкортоста</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>новости башкирии, командование, новости башкирии, стерлитамак новости, гладков белгород</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>мимо</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
+        <v>2115</v>
+      </c>
+      <c r="H36" t="n">
         <v>25</v>
       </c>
-      <c r="G36" t="n">
-        <v>2721</v>
-      </c>
-      <c r="H36" t="n">
-        <v>8</v>
-      </c>
       <c r="I36" t="n">
-        <v>5500</v>
+        <v>5900</v>
       </c>
       <c r="J36" t="n">
         <v>0.88</v>
@@ -2091,21 +2089,21 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bm24.ru</t>
+          <t>ecoportal.info</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Главная</t>
+          <t>Экологический портал - ECOportal.info | Сайт об экологии, растительном</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>рождество николая чудотворца, иоанн шанхайский, нечаянная радость икона, зерновой элеватор, день владимирской иконы</t>
+          <t>хищные птицы беларуси, гиена, амазонка животные, травоядные животные, птицы подмосковья</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2114,43 +2112,43 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G37" t="n">
-        <v>2115</v>
+        <v>10330</v>
       </c>
       <c r="H37" t="n">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="I37" t="n">
-        <v>5900</v>
+        <v>6700</v>
       </c>
       <c r="J37" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>ссылки открыты</t>
+          <t>размещений в выборке нет — просить пример</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ecoportal.info</t>
+          <t>globalkras.ru</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Экологический портал - ECOportal.info | Сайт об экологии, растительном</t>
+          <t>ГлобалКРАС.ру: Можно ли заработать на монетах из драгметаллов - Красно</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>хищные птицы беларуси, гиена, амазонка животные, травоядные животные, птицы подмосковья</t>
+          <t>гороскоп близнецы, гороскоп весы, гороскоп рак, гороскоп близнецы на сегодня, гороскоп лев</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2159,43 +2157,43 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>10330</v>
+        <v>2466</v>
       </c>
       <c r="H38" t="n">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="I38" t="n">
-        <v>6700</v>
+        <v>7000</v>
       </c>
       <c r="J38" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>размещений в выборке нет — просить пример</t>
+          <t>ссылки открыты</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>globalkras.ru</t>
+          <t>vremya.press</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ГлобалКРАС.ру: Можно ли заработать на монетах из драгметаллов - Красно</t>
+          <t>Главные новости Урфо, России и мира сегодня - Время PRESS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>гороскоп близнецы, гороскоп весы, гороскоп рак, гороскоп близнецы на сегодня, гороскоп лев</t>
+          <t>удар возмездия по украине, новости дня сегодня, в крыму ужасная трагедия сегодня, прописка, с 1 июля</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2204,13 +2202,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G39" t="n">
-        <v>2466</v>
+        <v>2548</v>
       </c>
       <c r="H39" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="I39" t="n">
         <v>7000</v>
@@ -2226,21 +2224,21 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>vremya.press</t>
+          <t>prostudio.ru</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Главные новости Урфо, России и мира сегодня - Время PRESS</t>
+          <t>Digital-агентство Prostudio — Ваш проводник в диджитал</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>удар возмездия по украине, новости дня сегодня, в крыму ужасная трагедия сегодня, прописка, с 1 июля</t>
+          <t>краш это, поколения по годам, сравнение текстов, краш, сравнение текстов онлайн</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2249,19 +2247,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G40" t="n">
-        <v>2548</v>
+        <v>7194</v>
       </c>
       <c r="H40" t="n">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="I40" t="n">
-        <v>7000</v>
+        <v>5990</v>
       </c>
       <c r="J40" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2270,96 +2268,51 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>41</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prostudio.ru</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Digital-агентство Prostudio — Ваш проводник в диджитал</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>краш это, поколения по годам, сравнение текстов, краш, сравнение текстов онлайн</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>мимо</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>39</v>
-      </c>
-      <c r="G41" t="n">
-        <v>7194</v>
-      </c>
-      <c r="H41" t="n">
-        <v>177</v>
-      </c>
-      <c r="I41" t="n">
-        <v>5990</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>ссылки открыты</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A41" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>fgisrf.ru</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Справочник расценок #1</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>ферм, установка окон пвх расценка в смете, демонтаж плинтуса расценка в смете, демонтаж кирпичной кладки смета, рас</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>смежная</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F41" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>2059</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I41" s="2" t="n">
         <v>2600</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="J41" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>размещений в выборке нет — просить пример</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5563,7 +5516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5877,6 +5830,142 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>donnews.ru</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>уже оплачено</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>размещение оплачено на бирже, повтор не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>energyland.info</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>уже оплачено</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>размещение оплачено на бирже, повтор не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>factories.by</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>уже оплачено</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>размещение оплачено на бирже, повтор не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>info-svarka.ru</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>уже оплачено</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>размещение оплачено на бирже, повтор не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>miniteh.com</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>уже оплачено</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>размещение оплачено на бирже, повтор не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>oborudunion.ru</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>уже оплачено</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>размещение оплачено на бирже, повтор не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>rlocman.ru</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>уже оплачено</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>размещение оплачено на бирже, повтор не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ssa.ru</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>уже оплачено</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>размещение оплачено на бирже, повтор не нужен</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
